--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -3,17 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$B$55</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$B$66</definedName>
   </definedNames>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="8LZpkO9jbhKR0VcVEJ20nPKUTzE2zwDZKCDGS7yvyiY="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="199">
   <si>
     <t>id propuesto</t>
   </si>
@@ -24,16 +29,22 @@
     <t>shp</t>
   </si>
   <si>
+    <t>Sinonimos</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
     <t>ani_001</t>
   </si>
   <si>
     <t>pez</t>
   </si>
   <si>
-    <t>waka</t>
-  </si>
-  <si>
-    <t>huaca</t>
+    <t>yapa (pescado vivo)</t>
+  </si>
+  <si>
+    <t>piti (pescado cocinado)</t>
   </si>
   <si>
     <t>ani_002</t>
@@ -42,10 +53,10 @@
     <t>tortuga</t>
   </si>
   <si>
-    <t>shahue</t>
-  </si>
-  <si>
-    <t>Mana sahue</t>
+    <t>mananxao</t>
+  </si>
+  <si>
+    <t>kabori (tortuga de agua)</t>
   </si>
   <si>
     <t>ani_003</t>
@@ -57,25 +68,19 @@
     <t>ochiti</t>
   </si>
   <si>
-    <t>uchete</t>
-  </si>
-  <si>
     <t>ani_004</t>
   </si>
   <si>
     <t>mono</t>
   </si>
   <si>
-    <t>hiso</t>
-  </si>
-  <si>
-    <t>hisocuru</t>
-  </si>
-  <si>
-    <t>huasa</t>
-  </si>
-  <si>
-    <t>ku</t>
+    <t>shino</t>
+  </si>
+  <si>
+    <t>joxo shino (colorado)</t>
+  </si>
+  <si>
+    <t>forma más general de decir mono (shino)</t>
   </si>
   <si>
     <t>ani_005</t>
@@ -96,180 +101,129 @@
     <t>rono</t>
   </si>
   <si>
+    <t>ani_007</t>
+  </si>
+  <si>
+    <t>jaguar</t>
+  </si>
+  <si>
+    <t>kape</t>
+  </si>
+  <si>
+    <t>ani_008</t>
+  </si>
+  <si>
+    <t>caimán</t>
+  </si>
+  <si>
+    <t>ani_009</t>
+  </si>
+  <si>
+    <t>pato</t>
+  </si>
+  <si>
+    <t>nonon</t>
+  </si>
+  <si>
+    <t>ani_010</t>
+  </si>
+  <si>
+    <t>gallina</t>
+  </si>
+  <si>
+    <t>atapa</t>
+  </si>
+  <si>
+    <t>ani_011</t>
+  </si>
+  <si>
+    <t>mariposa</t>
+  </si>
+  <si>
+    <t>penpen</t>
+  </si>
+  <si>
+    <t>ani_012</t>
+  </si>
+  <si>
+    <t>venado</t>
+  </si>
+  <si>
+    <t>chasho</t>
+  </si>
+  <si>
+    <t>ani_013</t>
+  </si>
+  <si>
+    <t>gato</t>
+  </si>
+  <si>
+    <t>misho</t>
+  </si>
+  <si>
+    <t>mishito</t>
+  </si>
+  <si>
+    <t>col_001</t>
+  </si>
+  <si>
+    <t>blanco</t>
+  </si>
+  <si>
+    <t>osho</t>
+  </si>
+  <si>
+    <t>col_002</t>
+  </si>
+  <si>
+    <t>negro</t>
+  </si>
+  <si>
+    <t>wiso</t>
+  </si>
+  <si>
+    <t>col_003</t>
+  </si>
+  <si>
+    <t>azul</t>
+  </si>
+  <si>
+    <t>yakon</t>
+  </si>
+  <si>
+    <t>col_004</t>
+  </si>
+  <si>
+    <t>rojo</t>
+  </si>
+  <si>
+    <t>yoshin</t>
+  </si>
+  <si>
+    <t>col_005</t>
+  </si>
+  <si>
+    <t>verde</t>
+  </si>
+  <si>
+    <t>col_006</t>
+  </si>
+  <si>
+    <t>amarillo</t>
+  </si>
+  <si>
+    <t>panshin</t>
+  </si>
+  <si>
+    <t>col_007</t>
+  </si>
+  <si>
+    <t>gris</t>
+  </si>
+  <si>
     <t>no hay</t>
   </si>
   <si>
-    <t>ani_007</t>
-  </si>
-  <si>
-    <t>jaguar</t>
-  </si>
-  <si>
-    <t>ino</t>
-  </si>
-  <si>
-    <t>ani_008</t>
-  </si>
-  <si>
-    <t>caimán</t>
-  </si>
-  <si>
-    <t>cape</t>
-  </si>
-  <si>
-    <t>ani_009</t>
-  </si>
-  <si>
-    <t>pato</t>
-  </si>
-  <si>
-    <t>ana</t>
-  </si>
-  <si>
-    <t>nunu</t>
-  </si>
-  <si>
-    <t>ani_010</t>
-  </si>
-  <si>
-    <t>gallina</t>
-  </si>
-  <si>
-    <t>atapa</t>
-  </si>
-  <si>
-    <t>Attapa ahui</t>
-  </si>
-  <si>
-    <t>ani_011</t>
-  </si>
-  <si>
-    <t>mariposa</t>
-  </si>
-  <si>
-    <t>penpen</t>
-  </si>
-  <si>
-    <t>uso</t>
-  </si>
-  <si>
-    <t>Puempue</t>
-  </si>
-  <si>
-    <t>ani_012</t>
-  </si>
-  <si>
-    <t>venado</t>
-  </si>
-  <si>
-    <t>chaso</t>
-  </si>
-  <si>
-    <t>Schazu</t>
-  </si>
-  <si>
-    <t>ani_013</t>
-  </si>
-  <si>
-    <t>gato</t>
-  </si>
-  <si>
-    <t>misho</t>
-  </si>
-  <si>
-    <t>mishito</t>
-  </si>
-  <si>
-    <t>mishora</t>
-  </si>
-  <si>
-    <t>Sufejuimís Michi</t>
-  </si>
-  <si>
-    <t>col_001</t>
-  </si>
-  <si>
-    <t>blanco</t>
-  </si>
-  <si>
-    <t>josho</t>
-  </si>
-  <si>
-    <t>usu</t>
-  </si>
-  <si>
-    <t>col_002</t>
-  </si>
-  <si>
-    <t>negro</t>
-  </si>
-  <si>
-    <t>wiso</t>
-  </si>
-  <si>
-    <t>Huiso</t>
-  </si>
-  <si>
-    <t>Chese</t>
-  </si>
-  <si>
-    <t>col_003</t>
-  </si>
-  <si>
-    <t>azul</t>
-  </si>
-  <si>
-    <t>sankon</t>
-  </si>
-  <si>
-    <t>yancun</t>
-  </si>
-  <si>
-    <t>col_004</t>
-  </si>
-  <si>
-    <t>rojo</t>
-  </si>
-  <si>
-    <t>waschi</t>
-  </si>
-  <si>
-    <t>Huaschi</t>
-  </si>
-  <si>
-    <t>col_005</t>
-  </si>
-  <si>
-    <t>verde</t>
-  </si>
-  <si>
-    <t>joshin</t>
-  </si>
-  <si>
-    <t>Pása</t>
-  </si>
-  <si>
-    <t>col_006</t>
-  </si>
-  <si>
-    <t>amarillo</t>
-  </si>
-  <si>
-    <t>panshin</t>
-  </si>
-  <si>
-    <t>Panschi</t>
-  </si>
-  <si>
-    <t>col_007</t>
-  </si>
-  <si>
-    <t>gris</t>
-  </si>
-  <si>
-    <t>coro</t>
-  </si>
-  <si>
     <t>col_008</t>
   </si>
   <si>
@@ -282,19 +236,19 @@
     <t>rosado</t>
   </si>
   <si>
+    <t>col_010</t>
+  </si>
+  <si>
+    <t>morado</t>
+  </si>
+  <si>
     <t>cuer_001</t>
   </si>
   <si>
     <t>mano</t>
   </si>
   <si>
-    <t>meno</t>
-  </si>
-  <si>
-    <t>Muecayao (mano derecha)</t>
-  </si>
-  <si>
-    <t>Muemio (mano izquierda)</t>
+    <t>meken</t>
   </si>
   <si>
     <t>cuer_002</t>
@@ -306,19 +260,13 @@
     <t>kesha</t>
   </si>
   <si>
-    <t>Quesa</t>
-  </si>
-  <si>
     <t>cuer_003</t>
   </si>
   <si>
     <t>ojo</t>
   </si>
   <si>
-    <t>wero</t>
-  </si>
-  <si>
-    <t>Buero</t>
+    <t>bero</t>
   </si>
   <si>
     <t>cuer_004</t>
@@ -330,9 +278,6 @@
     <t>mapo</t>
   </si>
   <si>
-    <t>Mapu</t>
-  </si>
-  <si>
     <t>cuer_005</t>
   </si>
   <si>
@@ -348,10 +293,7 @@
     <t>corazón</t>
   </si>
   <si>
-    <t>humti</t>
-  </si>
-  <si>
-    <t>Humti</t>
+    <t>jointi</t>
   </si>
   <si>
     <t>cuer_007</t>
@@ -363,19 +305,13 @@
     <t>boo</t>
   </si>
   <si>
-    <t>bu</t>
-  </si>
-  <si>
     <t>cuer_008</t>
   </si>
   <si>
     <t>diente</t>
   </si>
   <si>
-    <t>seta</t>
-  </si>
-  <si>
-    <t>Ceta</t>
+    <t>sheta</t>
   </si>
   <si>
     <t>cuer_009</t>
@@ -384,7 +320,7 @@
     <t>nariz</t>
   </si>
   <si>
-    <t>singa</t>
+    <t>rekin</t>
   </si>
   <si>
     <t>cuer_010</t>
@@ -393,7 +329,7 @@
     <t>oreja</t>
   </si>
   <si>
-    <t>Pabiqui</t>
+    <t>pabiki</t>
   </si>
   <si>
     <t>cuer_011</t>
@@ -402,10 +338,7 @@
     <t>brazo</t>
   </si>
   <si>
-    <t>pon</t>
-  </si>
-  <si>
-    <t>Puya</t>
+    <t>poyan</t>
   </si>
   <si>
     <t>cuer_012</t>
@@ -414,10 +347,7 @@
     <t>pierna</t>
   </si>
   <si>
-    <t>witas</t>
-  </si>
-  <si>
-    <t>huitas</t>
+    <t>kishi</t>
   </si>
   <si>
     <t>nat_001</t>
@@ -426,10 +356,7 @@
     <t>agua</t>
   </si>
   <si>
-    <t>jene</t>
-  </si>
-  <si>
-    <t>Umpas</t>
+    <t>onpax</t>
   </si>
   <si>
     <t>nat_002</t>
@@ -441,19 +368,13 @@
     <t>bari</t>
   </si>
   <si>
-    <t>Bari</t>
-  </si>
-  <si>
     <t>nat_003</t>
   </si>
   <si>
     <t>árbol</t>
   </si>
   <si>
-    <t>jihui</t>
-  </si>
-  <si>
-    <t>hibi</t>
+    <t>jiwi</t>
   </si>
   <si>
     <t>nat_004</t>
@@ -462,10 +383,7 @@
     <t>luna</t>
   </si>
   <si>
-    <t>oshi</t>
-  </si>
-  <si>
-    <t>use</t>
+    <t>oshe</t>
   </si>
   <si>
     <t>nat_005</t>
@@ -474,10 +392,7 @@
     <t>río</t>
   </si>
   <si>
-    <t>hene</t>
-  </si>
-  <si>
-    <t>Hene</t>
+    <t>paro</t>
   </si>
   <si>
     <t>nat_006</t>
@@ -489,16 +404,13 @@
     <t>niwe</t>
   </si>
   <si>
-    <t>Nihue</t>
-  </si>
-  <si>
     <t>nat_007</t>
   </si>
   <si>
     <t>lluvia</t>
   </si>
   <si>
-    <t>hui</t>
+    <t>oi</t>
   </si>
   <si>
     <t>nat_008</t>
@@ -507,10 +419,7 @@
     <t>nube</t>
   </si>
   <si>
-    <t>wischni</t>
-  </si>
-  <si>
-    <t>Huischni</t>
+    <t>koin</t>
   </si>
   <si>
     <t>nat_009</t>
@@ -519,10 +428,7 @@
     <t>fuego</t>
   </si>
   <si>
-    <t>chi</t>
-  </si>
-  <si>
-    <t>Chi</t>
+    <t>chii</t>
   </si>
   <si>
     <t>nat_010</t>
@@ -540,10 +446,7 @@
     <t>noche</t>
   </si>
   <si>
-    <t>yamé</t>
-  </si>
-  <si>
-    <t>Yammue</t>
+    <t>yame</t>
   </si>
   <si>
     <t>obj_001</t>
@@ -555,9 +458,6 @@
     <t>nonti</t>
   </si>
   <si>
-    <t>Nunti</t>
-  </si>
-  <si>
     <t>obj_002</t>
   </si>
   <si>
@@ -567,19 +467,13 @@
     <t>shobo</t>
   </si>
   <si>
-    <t>Sobo</t>
-  </si>
-  <si>
     <t>obj_003</t>
   </si>
   <si>
     <t>olla</t>
   </si>
   <si>
-    <t>chomo</t>
-  </si>
-  <si>
-    <t>Quenti</t>
+    <t>yamikenti</t>
   </si>
   <si>
     <t>obj_004</t>
@@ -588,10 +482,7 @@
     <t>tela</t>
   </si>
   <si>
-    <t>chupa</t>
-  </si>
-  <si>
-    <t>Chupa</t>
+    <t>chopa</t>
   </si>
   <si>
     <t>obj_005</t>
@@ -603,28 +494,19 @@
     <t>piti</t>
   </si>
   <si>
-    <t>Nahuiti</t>
-  </si>
-  <si>
     <t>obj_006</t>
   </si>
   <si>
     <t>ropa</t>
   </si>
   <si>
-    <t>chaira</t>
-  </si>
-  <si>
     <t>obj_007</t>
   </si>
   <si>
     <t>plato</t>
   </si>
   <si>
-    <t>kencha</t>
-  </si>
-  <si>
-    <t>Quencha Quempo</t>
+    <t>paranta</t>
   </si>
   <si>
     <t>obj_008</t>
@@ -642,14 +524,104 @@
     <t>escuela</t>
   </si>
   <si>
-    <t>kirika shobo</t>
+    <t>jainoax asheti</t>
+  </si>
+  <si>
+    <t>num_001</t>
+  </si>
+  <si>
+    <t>uno</t>
+  </si>
+  <si>
+    <t>westiora</t>
+  </si>
+  <si>
+    <t>num_002</t>
+  </si>
+  <si>
+    <t>dos</t>
+  </si>
+  <si>
+    <t>rabe</t>
+  </si>
+  <si>
+    <t>num_003</t>
+  </si>
+  <si>
+    <t>tres</t>
+  </si>
+  <si>
+    <t>kimisha</t>
+  </si>
+  <si>
+    <t>num_004</t>
+  </si>
+  <si>
+    <t>cuatro</t>
+  </si>
+  <si>
+    <t>chosko</t>
+  </si>
+  <si>
+    <t>num_005</t>
+  </si>
+  <si>
+    <t>cinco</t>
+  </si>
+  <si>
+    <t>pishika</t>
+  </si>
+  <si>
+    <t>num_006</t>
+  </si>
+  <si>
+    <t>seis</t>
+  </si>
+  <si>
+    <t>sokota</t>
+  </si>
+  <si>
+    <t>num_007</t>
+  </si>
+  <si>
+    <t>siete</t>
+  </si>
+  <si>
+    <t>canchis</t>
+  </si>
+  <si>
+    <t>num_008</t>
+  </si>
+  <si>
+    <t>ocho</t>
+  </si>
+  <si>
+    <t>sotoka</t>
+  </si>
+  <si>
+    <t>num_009</t>
+  </si>
+  <si>
+    <t>nueve</t>
+  </si>
+  <si>
+    <t>posoka</t>
+  </si>
+  <si>
+    <t>num_010</t>
+  </si>
+  <si>
+    <t>diez</t>
+  </si>
+  <si>
+    <t>chonka</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -658,6 +630,7 @@
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
@@ -667,7 +640,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -676,7 +654,7 @@
       <name val="Verdana"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,24 +669,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6FA8DC"/>
-        <bgColor rgb="FF6FA8DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAEAEA"/>
-        <bgColor rgb="FFEAEAEA"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F1F1"/>
+        <bgColor rgb="FFF1F1F1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -724,31 +708,51 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,10 +764,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,10 +964,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="3" max="3" width="15.88"/>
+    <col customWidth="1" min="4" max="4" width="18.13"/>
+    <col customWidth="1" min="5" max="6" width="12.63"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,787 +984,1683 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="4" t="s">
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="5" t="s">
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="4" t="s">
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="4" t="s">
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="4" t="s">
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="5" t="s">
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="4" t="s">
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="C22" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C23" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+      <c r="C24" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="5" t="s">
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="4" t="s">
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="5" t="s">
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="B32" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="C32" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B33" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="5" t="s">
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+      <c r="B34" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="4" t="s">
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="B36" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="B37" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B38" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="4" t="s">
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+      <c r="B39" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="4" t="s">
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="B40" s="7" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="B41" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B33" s="3" t="s">
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="B42" s="7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B34" s="3" t="s">
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="B43" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="C43" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B44" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="4" t="s">
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="7" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+      <c r="B45" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="4" t="s">
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="B46" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="3" t="s">
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="B47" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="C47" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B48" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="4" t="s">
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="7" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+      <c r="B49" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C39" s="4" t="s">
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="B50" s="7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B40" s="3" t="s">
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="B51" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="C51" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B52" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D41" s="5" t="s">
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
+      <c r="B53" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C53" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="B54" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B43" s="3" t="s">
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="B55" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="C55" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B56" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="5" t="s">
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C45" s="4" t="s">
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C46" s="4" t="s">
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="B59" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="C60" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D48" s="5" t="s">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="4" t="s">
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="B63" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="3" t="s">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="C64" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D51" s="5" t="s">
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
+    </row>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$B$55">
-    <sortState ref="A1:B55">
-      <sortCondition ref="A1:A55"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="$A$1:$B$66"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="9" min="1" max="2"/>
@@ -1845,22 +1845,22 @@
     <row r="78" ht="15.75" customHeight="1" s="9">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>acc_001</t>
+          <t>nat_012</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>cazar</t>
+          <t>cocha</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>yomerati</t>
+          <t>ian</t>
         </is>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
-          <t>buscar/pescar</t>
+          <t>laguna</t>
         </is>
       </c>
       <c r="E78" s="0" t="inlineStr">
@@ -1872,17 +1872,22 @@
     <row r="79" ht="15.75" customHeight="1" s="9">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>acc_002</t>
+          <t>obj_010</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>amarrar</t>
+          <t>masato</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>nexati</t>
+          <t>atsa</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>bebida de yuca</t>
         </is>
       </c>
       <c r="E79" s="0" t="inlineStr">
@@ -1894,17 +1899,17 @@
     <row r="80" ht="15.75" customHeight="1" s="9">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>acc_003</t>
+          <t>obj_011</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>asustarse</t>
+          <t>fiesta</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>rateti</t>
+          <t>pishta</t>
         </is>
       </c>
       <c r="E80" s="0" t="inlineStr">
@@ -1913,251 +1918,16 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1" s="9">
-      <c r="A81" s="0" t="inlineStr">
-        <is>
-          <t>acc_004</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="inlineStr">
-        <is>
-          <t>insultar</t>
-        </is>
-      </c>
-      <c r="C81" s="0" t="inlineStr">
-        <is>
-          <t>ichati</t>
-        </is>
-      </c>
-      <c r="E81" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" s="9">
-      <c r="A82" s="0" t="inlineStr">
-        <is>
-          <t>acc_005</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t>desatar</t>
-        </is>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>choroti</t>
-        </is>
-      </c>
-      <c r="E82" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" s="9">
-      <c r="A83" s="0" t="inlineStr">
-        <is>
-          <t>acc_006</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="inlineStr">
-        <is>
-          <t>enamorarse</t>
-        </is>
-      </c>
-      <c r="C83" s="0" t="inlineStr">
-        <is>
-          <t>merati</t>
-        </is>
-      </c>
-      <c r="E83" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" s="9">
-      <c r="A84" s="0" t="inlineStr">
-        <is>
-          <t>nat_012</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>cocha</t>
-        </is>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>ian</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="inlineStr">
-        <is>
-          <t>laguna</t>
-        </is>
-      </c>
-      <c r="E84" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="9">
-      <c r="A85" s="0" t="inlineStr">
-        <is>
-          <t>obj_010</t>
-        </is>
-      </c>
-      <c r="B85" s="0" t="inlineStr">
-        <is>
-          <t>masato</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="inlineStr">
-        <is>
-          <t>atsa</t>
-        </is>
-      </c>
-      <c r="D85" s="0" t="inlineStr">
-        <is>
-          <t>bebida de yuca</t>
-        </is>
-      </c>
-      <c r="E85" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="9">
-      <c r="A86" s="0" t="inlineStr">
-        <is>
-          <t>obj_011</t>
-        </is>
-      </c>
-      <c r="B86" s="0" t="inlineStr">
-        <is>
-          <t>fiesta</t>
-        </is>
-      </c>
-      <c r="C86" s="0" t="inlineStr">
-        <is>
-          <t>pishta</t>
-        </is>
-      </c>
-      <c r="E86" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="9">
-      <c r="A87" s="0" t="inlineStr">
-        <is>
-          <t>cua_001</t>
-        </is>
-      </c>
-      <c r="B87" s="0" t="inlineStr">
-        <is>
-          <t>mucho</t>
-        </is>
-      </c>
-      <c r="C87" s="0" t="inlineStr">
-        <is>
-          <t>icha</t>
-        </is>
-      </c>
-      <c r="D87" s="0" t="inlineStr">
-        <is>
-          <t>muchos</t>
-        </is>
-      </c>
-      <c r="E87" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" s="9">
-      <c r="A88" s="0" t="inlineStr">
-        <is>
-          <t>cua_002</t>
-        </is>
-      </c>
-      <c r="B88" s="0" t="inlineStr">
-        <is>
-          <t>borracho</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="inlineStr">
-        <is>
-          <t>paena</t>
-        </is>
-      </c>
-      <c r="D88" s="0" t="inlineStr">
-        <is>
-          <t>mareado</t>
-        </is>
-      </c>
-      <c r="E88" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" s="9">
-      <c r="A89" s="0" t="inlineStr">
-        <is>
-          <t>cua_003</t>
-        </is>
-      </c>
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>rayas</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="inlineStr">
-        <is>
-          <t>chisereya</t>
-        </is>
-      </c>
-      <c r="D89" s="0" t="inlineStr">
-        <is>
-          <t>que tiene rayas</t>
-        </is>
-      </c>
-      <c r="E89" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" s="9">
-      <c r="A90" s="0" t="inlineStr">
-        <is>
-          <t>cua_004</t>
-        </is>
-      </c>
-      <c r="B90" s="0" t="inlineStr">
-        <is>
-          <t>hueco</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="inlineStr">
-        <is>
-          <t>kini</t>
-        </is>
-      </c>
-      <c r="E90" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
+    <row r="81" ht="15.75" customHeight="1" s="9"/>
+    <row r="82" ht="15.75" customHeight="1" s="9"/>
+    <row r="83" ht="15.75" customHeight="1" s="9"/>
+    <row r="84" ht="15.75" customHeight="1" s="9"/>
+    <row r="85" ht="15.75" customHeight="1" s="9"/>
+    <row r="86" ht="15.75" customHeight="1" s="9"/>
+    <row r="87" ht="15.75" customHeight="1" s="9"/>
+    <row r="88" ht="15.75" customHeight="1" s="9"/>
+    <row r="89" ht="15.75" customHeight="1" s="9"/>
+    <row r="90" ht="15.75" customHeight="1" s="9"/>
     <row r="91" ht="15.75" customHeight="1" s="9"/>
     <row r="92" ht="15.75" customHeight="1" s="9"/>
     <row r="93" ht="15.75" customHeight="1" s="9"/>

--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -713,7 +713,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>osho</t>
+          <t>joxo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -747,7 +752,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>yakon</t>
+          <t>yankon</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -764,7 +774,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>yoshin</t>
+          <t>joshin</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -781,7 +796,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>yakon</t>
+          <t>yankon</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1311,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>shobo</t>
+          <t>xobo</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1401,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>paranta</t>
+          <t>rato</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1440,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>jainoax asheti</t>
+          <t>jainoax axeti</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1531,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>pishika</t>
+          <t>pichika</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1570,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>canchis</t>
+          <t>kanchis</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1592,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>sotoka</t>
+          <t>posaka</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1614,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>posoka</t>
+          <t>iskon</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1937,7 @@
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>atsa</t>
+          <t>atsa xeati</t>
         </is>
       </c>
       <c r="D79" s="0" t="inlineStr">
@@ -1892,7 +1947,7 @@
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+          <t>PROPUESTA cuentos - validar con hablante | Corregido por validador</t>
         </is>
       </c>
     </row>

--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -589,7 +589,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>kape</t>
+          <t>ino</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): kape → ino.</t>
         </is>
       </c>
     </row>
@@ -674,7 +679,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>chasho</t>
+          <t>chaxo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): chasho → chaxo.</t>
         </is>
       </c>
     </row>
@@ -716,7 +726,7 @@
           <t>joxo</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -755,7 +765,7 @@
           <t>yankon</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -777,7 +787,7 @@
           <t>joshin</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -799,7 +809,7 @@
           <t>yankon</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -920,7 +930,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>kesha</t>
+          <t>kexa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): kesha → kexa.</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1037,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>sheta</t>
+          <t>xeta</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): sheta → xeta.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1178,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>oshe</t>
+          <t>oxe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): oshe → oxe.</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1339,7 @@
           <t>xobo</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1404,7 +1429,7 @@
           <t>rato</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1443,7 +1468,7 @@
           <t>jainoax axeti</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1534,7 +1559,7 @@
           <t>pichika</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1573,7 +1598,7 @@
           <t>kanchis</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1595,7 +1620,7 @@
           <t>posaka</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>
@@ -1617,7 +1642,7 @@
           <t>iskon</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>Corregido por validador</t>
         </is>

--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -489,12 +489,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>mananxao</t>
+          <t>kabori</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>kabori (tortuga de agua)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Corrección validador (retro): mananxao → kabori.</t>
         </is>
       </c>
     </row>
@@ -589,12 +594,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ino</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Corrección validador piloto (E3): kape → ino.</t>
+          <t>toto ino</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Corrección validador piloto (E3): kape → ino. Corrección validador (retro): ino → toto ino.</t>
         </is>
       </c>
     </row>
@@ -682,7 +687,7 @@
           <t>chaxo</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Corrección validador piloto (E3): chasho → chaxo.</t>
         </is>
@@ -933,7 +938,7 @@
           <t>kexa</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Corrección validador piloto (E3): kesha → kexa.</t>
         </is>
@@ -1040,7 +1045,7 @@
           <t>xeta</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>Corrección validador piloto (E3): sheta → xeta.</t>
         </is>
@@ -1181,7 +1186,7 @@
           <t>oxe</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>Corrección validador piloto (E3): oshe → oxe.</t>
         </is>
@@ -1409,7 +1414,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>chopa</t>
+          <t>saweti chopa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Corrección validador (retro): chopa → saweti chopa.</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1458,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>kirika</t>
+          <t>yoyo ati kirika</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Corrección validador (retro): kirika → yoyo ati kirika.</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1803,12 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>ino</t>
+          <t>sere ino</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): ino → sere ino.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1825,7 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>mananxawe</t>
+          <t>manan xawe</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
@@ -1820,7 +1835,7 @@
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): mananxawe → manan xawe.</t>
         </is>
       </c>
     </row>

--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -497,7 +497,7 @@
           <t>kabori (tortuga de agua)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Corrección validador (retro): mananxao → kabori.</t>
         </is>
@@ -811,12 +811,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>yankon</t>
+          <t>xoo</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>Corregido por validador</t>
+          <t>Corregido por validador Corrección validador: verde yankon → xoo (verde y azul son distintos en shipibo; ya no comparten forma).</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
           <t>saweti chopa</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>Corrección validador (retro): chopa → saweti chopa.</t>
         </is>
@@ -1461,7 +1461,7 @@
           <t>yoyo ati kirika</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>Corrección validador (retro): kirika → yoyo ati kirika.</t>
         </is>

--- a/actions/corpus/palabras.xlsx
+++ b/actions/corpus/palabras.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.63" customWidth="1" style="9" min="1" max="2"/>
@@ -811,12 +811,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>xoo</t>
+          <t>yankon</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>Corregido por validador Corrección validador: verde yankon → xoo (verde y azul son distintos en shipibo; ya no comparten forma).</t>
+          <t>Corregido por validador</t>
         </is>
       </c>
     </row>
@@ -1683,61 +1683,71 @@
     <row r="67" ht="15.75" customHeight="1" s="9">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>per_001</t>
+          <t>ani_014</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>hombre</t>
+          <t>tigre</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>joni</t>
+          <t>sere ino</t>
         </is>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): ino → sere ino.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="9">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>per_002</t>
+          <t>ani_015</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>cuñado</t>
+          <t>motelo</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>chai</t>
+          <t>manan xawe</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>tortuga terrestre</t>
         </is>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): mananxawe → manan xawe.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="9">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>per_003</t>
+          <t>ani_016</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>madre</t>
+          <t>paujil</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>tita</t>
+          <t>jasin</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>ave de la selva</t>
         </is>
       </c>
       <c r="E69" s="0" t="inlineStr">
@@ -1749,17 +1759,22 @@
     <row r="70" ht="15.75" customHeight="1" s="9">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>per_004</t>
+          <t>ani_017</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>señorita</t>
+          <t>camungo</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>xontako</t>
+          <t>abokoma</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>ave</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
@@ -1771,17 +1786,17 @@
     <row r="71" ht="15.75" customHeight="1" s="9">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>per_005</t>
+          <t>ani_018</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>hijos</t>
+          <t>zorro</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>bakebo</t>
+          <t>maxo</t>
         </is>
       </c>
       <c r="E71" s="0" t="inlineStr">
@@ -1793,232 +1808,338 @@
     <row r="72" ht="15.75" customHeight="1" s="9">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>ani_014</t>
+          <t>ani_019</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>tigre</t>
+          <t>loro</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>sere ino</t>
+          <t>bawa</t>
         </is>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): ino → sere ino.</t>
+          <t>PROPUESTA cuentos - validar con hablante</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="9">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>ani_015</t>
+          <t>nat_012</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>motelo</t>
+          <t>cocha</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>manan xawe</t>
+          <t>ian</t>
         </is>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>tortuga terrestre</t>
+          <t>laguna</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>PROPUESTA cuentos - validar con hablante Corrección validador (retro): mananxawe → manan xawe.</t>
+          <t>PROPUESTA cuentos - validar con hablante</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="9">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>ani_016</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>paujil</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>jasin</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="inlineStr">
-        <is>
-          <t>ave de la selva</t>
-        </is>
-      </c>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fam_001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>mamá</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>tita</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="9">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>ani_017</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>camungo</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>abokoma</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="inlineStr">
-        <is>
-          <t>ave</t>
-        </is>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fam_002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>papá</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="9">
-      <c r="A76" s="0" t="inlineStr">
-        <is>
-          <t>ani_018</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>zorro</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>maxo</t>
-        </is>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fam_003</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>hija</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ainbo bake</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="9">
-      <c r="A77" s="0" t="inlineStr">
-        <is>
-          <t>ani_019</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t>loro</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>bawa</t>
-        </is>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fam_004</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>hijo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>benbo bake</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="9">
-      <c r="A78" s="0" t="inlineStr">
-        <is>
-          <t>nat_012</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>cocha</t>
-        </is>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>ian</t>
-        </is>
-      </c>
-      <c r="D78" s="0" t="inlineStr">
-        <is>
-          <t>laguna</t>
-        </is>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fam_005</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>bebé</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>binshin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="9">
-      <c r="A79" s="0" t="inlineStr">
-        <is>
-          <t>obj_010</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>masato</t>
-        </is>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>atsa xeati</t>
-        </is>
-      </c>
-      <c r="D79" s="0" t="inlineStr">
-        <is>
-          <t>bebida de yuca</t>
-        </is>
-      </c>
-      <c r="E79" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante | Corregido por validador</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fam_006</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>abuela</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>yoxan</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="9">
-      <c r="A80" s="0" t="inlineStr">
-        <is>
-          <t>obj_011</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>fiesta</t>
-        </is>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>pishta</t>
-        </is>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t>PROPUESTA cuentos - validar con hablante</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="9"/>
-    <row r="82" ht="15.75" customHeight="1" s="9"/>
-    <row r="83" ht="15.75" customHeight="1" s="9"/>
-    <row r="84" ht="15.75" customHeight="1" s="9"/>
-    <row r="85" ht="15.75" customHeight="1" s="9"/>
-    <row r="86" ht="15.75" customHeight="1" s="9"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fam_007</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>abuelo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>yosi</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="9">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fam_008</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nieto</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>baba</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" s="9">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>fam_009</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>tío</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>koka</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="9">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>fam_010</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>tía</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>wata</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="9">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fam_011</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>wetsa</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="9">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fam_012</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hermano</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>wetsako</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="9">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>fam_013</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hermana</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>wetsa</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Categoría familia (reemplaza a personas). Aportado por validador.</t>
+        </is>
+      </c>
+    </row>
     <row r="87" ht="15.75" customHeight="1" s="9"/>
     <row r="88" ht="15.75" customHeight="1" s="9"/>
     <row r="89" ht="15.75" customHeight="1" s="9"/>
